--- a/reports/pdf_change_20261022.xlsx
+++ b/reports/pdf_change_20261022.xlsx
@@ -567,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 9/10  ·  전일분: TIGER 기술이전, TIGER 코스닥, MIDAS  ·  대기: RISE</t>
+          <t>캡처 9/10  ·  전일분: TIGER 기술이전, TIGER 코스닥, MIDAS  ·  대기: RISE  ·  검증필요 1건</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,470억   ·   현금 33억(0.7%)      당일 2026-10-22  vs  전영업일 2026-10-21      매수 8종목  /  매도 0종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,594억      당일 2026-10-22  vs  전영업일 2026-10-21      매수 8종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>52</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1330966696</v>
+        <v>1333644187</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>51</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>2331925220</v>
+        <v>2336616328</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>29</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1347616205</v>
+        <v>1350327190</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>21</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1333849298</v>
+        <v>1336532588</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>619063524</v>
+        <v>620308887</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2147041123</v>
+        <v>2151360302</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>850069245</v>
+        <v>851779320</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>748482392</v>
+        <v>749988105</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,109억   ·   현금 59억(1.9%)      당일 2026-10-22  vs  전영업일 2026-10-21      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,216억      당일 2026-10-22  vs  전영업일 2026-10-21      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -911,7 +911,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,290억   ·   현금 33억(1.4%)      당일 2026-10-22  vs  전영업일 2026-10-21      매수 9종목  /  매도 11종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,348억      당일 2026-10-22  vs  전영업일 2026-10-21      매수 9종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1007,7 +1007,7 @@
         <v>500</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>3140135858</v>
+        <v>3149665476</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>-113</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>-1155728156</v>
+        <v>-1159235535</v>
       </c>
       <c r="J21" s="18" t="inlineStr">
         <is>
@@ -1044,14 +1044,16 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>씨어스  (신규)</t>
+          <t>씨어스  (신규) ※검증필요</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>300</v>
       </c>
-      <c r="C22" s="11" t="n">
-        <v>4547101242</v>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>검증필요</t>
+        </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1072,7 +1074,7 @@
         <v>-108</v>
       </c>
       <c r="I22" s="17" t="n">
-        <v>-2761474354</v>
+        <v>-2769854819</v>
       </c>
       <c r="J22" s="18" t="inlineStr">
         <is>
@@ -1095,7 +1097,7 @@
         <v>251</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>6963720802</v>
+        <v>6984854157</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1116,7 +1118,7 @@
         <v>-50</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>-2112095577</v>
+        <v>-2118505320</v>
       </c>
       <c r="J23" s="18" t="inlineStr">
         <is>
@@ -1139,7 +1141,7 @@
         <v>152</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>1433404472</v>
+        <v>1437754538</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1160,7 +1162,7 @@
         <v>-50</v>
       </c>
       <c r="I24" s="17" t="n">
-        <v>-2738145748</v>
+        <v>-2746455416</v>
       </c>
       <c r="J24" s="18" t="inlineStr">
         <is>
@@ -1183,7 +1185,7 @@
         <v>150</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>6346171733</v>
+        <v>6365430963</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1204,7 +1206,7 @@
         <v>-43</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>-2366140146</v>
+        <v>-2373320859</v>
       </c>
       <c r="J25" s="18" t="inlineStr">
         <is>
@@ -1227,7 +1229,7 @@
         <v>100</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>2385580652</v>
+        <v>2392820362</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
@@ -1241,23 +1243,23 @@
       </c>
       <c r="G26" s="16" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H26" s="17" t="n">
         <v>-40</v>
       </c>
       <c r="I26" s="17" t="n">
-        <v>-3165836865</v>
+        <v>-7191681088</v>
       </c>
       <c r="J26" s="18" t="inlineStr">
         <is>
-          <t>4.46%→3.09%</t>
+          <t>4.62%→1.55%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>130→90</t>
+          <t>60→20</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1273,7 @@
         <v>85</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>1170713820</v>
+        <v>1174266678</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1285,23 +1287,23 @@
       </c>
       <c r="G27" s="16" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H27" s="17" t="n">
         <v>-40</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>-7169921958</v>
+        <v>-3175444480</v>
       </c>
       <c r="J27" s="18" t="inlineStr">
         <is>
-          <t>4.62%→1.55%</t>
+          <t>4.46%→3.09%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>60→20</t>
+          <t>130→90</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1317,7 @@
         <v>61</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>5065075383</v>
+        <v>5080446769</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1336,7 +1338,7 @@
         <v>-24</v>
       </c>
       <c r="I28" s="17" t="n">
-        <v>-3819565043</v>
+        <v>-3831156580</v>
       </c>
       <c r="J28" s="18" t="inlineStr">
         <is>
@@ -1359,7 +1361,7 @@
         <v>50</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>2632705719</v>
+        <v>2640695400</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1380,7 +1382,7 @@
         <v>-16</v>
       </c>
       <c r="I29" s="17" t="n">
-        <v>-4533921238</v>
+        <v>-4547680688</v>
       </c>
       <c r="J29" s="18" t="inlineStr">
         <is>
@@ -1408,7 +1410,7 @@
         <v>-14</v>
       </c>
       <c r="I30" s="17" t="n">
-        <v>-1471547402</v>
+        <v>-1476013223</v>
       </c>
       <c r="J30" s="18" t="inlineStr">
         <is>
@@ -1436,7 +1438,7 @@
         <v>-7</v>
       </c>
       <c r="I31" s="17" t="n">
-        <v>-1725262471</v>
+        <v>-1730498262</v>
       </c>
       <c r="J31" s="18" t="inlineStr">
         <is>
@@ -1452,7 +1454,7 @@
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,073억   ·   현금 5억(0.2%)      당일 2026-10-22  vs  전영업일 2026-10-21      매수 2종목  /  매도 1종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,142억      당일 2026-10-22  vs  전영업일 2026-10-21      매수 2종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
@@ -1548,7 +1550,7 @@
         <v>105</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>1078392385</v>
+        <v>1083894000</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1569,7 +1571,7 @@
         <v>-59</v>
       </c>
       <c r="I36" s="17" t="n">
-        <v>-957499542</v>
+        <v>-962384400</v>
       </c>
       <c r="J36" s="18" t="inlineStr">
         <is>
@@ -1592,7 +1594,7 @@
         <v>5</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>387296138</v>
+        <v>389272000</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1613,7 +1615,7 @@
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 269억   ·   현금 2억(0.9%)      당일 2026-10-22  vs  전영업일 2026-10-21      매수 2종목  /  매도 0종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 258억      당일 2026-10-22  vs  전영업일 2026-10-21      매수 2종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B39" s="4" t="n"/>
@@ -1709,11 +1711,11 @@
         <v>67</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>43318863</v>
+        <v>38763520</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>7.42%→7.56%</t>
+          <t>6.93%→7.06%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -1737,11 +1739,11 @@
         <v>14</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>35784711</v>
+        <v>30464000</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>7.78%→7.89%</t>
+          <t>6.92%→7.02%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -1799,7 +1801,7 @@
     <row r="50" ht="19" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 835억   ·   현금 3억(0.3%)      당일 2026-10-22  vs  전영업일 2026-10-21      매수 6종목  /  매도 9종목</t>
+          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 863억      당일 2026-10-22  vs  전영업일 2026-10-21      매수 6종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B50" s="4" t="n"/>
@@ -1895,7 +1897,7 @@
         <v>558</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>1252799127</v>
+        <v>1260438300</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
@@ -1916,7 +1918,7 @@
         <v>-187</v>
       </c>
       <c r="I53" s="17" t="n">
-        <v>-834169498</v>
+        <v>-839256000</v>
       </c>
       <c r="J53" s="18" t="inlineStr">
         <is>
@@ -1939,7 +1941,7 @@
         <v>96</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>664396719</v>
+        <v>668448000</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
@@ -1960,7 +1962,7 @@
         <v>-154</v>
       </c>
       <c r="I54" s="17" t="n">
-        <v>-354846757</v>
+        <v>-357010500</v>
       </c>
       <c r="J54" s="18" t="inlineStr">
         <is>
@@ -1983,7 +1985,7 @@
         <v>87</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>369541155</v>
+        <v>371794500</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
@@ -2004,7 +2006,7 @@
         <v>-109</v>
       </c>
       <c r="I55" s="17" t="n">
-        <v>-282440766</v>
+        <v>-284163000</v>
       </c>
       <c r="J55" s="18" t="inlineStr">
         <is>
@@ -2027,7 +2029,7 @@
         <v>74</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>333739959</v>
+        <v>335775000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
@@ -2048,7 +2050,7 @@
         <v>-96</v>
       </c>
       <c r="I56" s="17" t="n">
-        <v>-237734371</v>
+        <v>-239184000</v>
       </c>
       <c r="J56" s="18" t="inlineStr">
         <is>
@@ -2071,7 +2073,7 @@
         <v>32</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>228287972</v>
+        <v>229680000</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
@@ -2092,7 +2094,7 @@
         <v>-91</v>
       </c>
       <c r="I57" s="17" t="n">
-        <v>-406678950</v>
+        <v>-409158750</v>
       </c>
       <c r="J57" s="18" t="inlineStr">
         <is>
@@ -2115,7 +2117,7 @@
         <v>6</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>318323961</v>
+        <v>320265000</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
@@ -2136,7 +2138,7 @@
         <v>-19</v>
       </c>
       <c r="I58" s="17" t="n">
-        <v>-392615952</v>
+        <v>-395010000</v>
       </c>
       <c r="J58" s="18" t="inlineStr">
         <is>
@@ -2164,7 +2166,7 @@
         <v>-17</v>
       </c>
       <c r="I59" s="17" t="n">
-        <v>-181498778</v>
+        <v>-182605500</v>
       </c>
       <c r="J59" s="18" t="inlineStr">
         <is>
@@ -2192,7 +2194,7 @@
         <v>-15</v>
       </c>
       <c r="I60" s="17" t="n">
-        <v>-168263979</v>
+        <v>-169290000</v>
       </c>
       <c r="J60" s="18" t="inlineStr">
         <is>
@@ -2220,7 +2222,7 @@
         <v>-4</v>
       </c>
       <c r="I61" s="17" t="n">
-        <v>-282079966</v>
+        <v>-283800000</v>
       </c>
       <c r="J61" s="18" t="inlineStr">
         <is>
@@ -2332,11 +2334,11 @@
         <v>19</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>311685500</v>
+        <v>277780000</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>4.51%→5.47%</t>
+          <t>3.94%→4.78%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
@@ -2353,11 +2355,11 @@
         <v>-27</v>
       </c>
       <c r="I66" s="17" t="n">
-        <v>-134211600</v>
+        <v>-134095500</v>
       </c>
       <c r="J66" s="18" t="inlineStr">
         <is>
-          <t>1.50%→1.03%</t>
+          <t>1.47%→1.01%</t>
         </is>
       </c>
       <c r="K66" s="13" t="inlineStr">
@@ -2376,11 +2378,11 @@
         <v>18</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>332046000</v>
+        <v>356040000</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.10%</t>
+          <t>0.00%→1.15%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
@@ -2397,11 +2399,11 @@
         <v>-24</v>
       </c>
       <c r="I67" s="17" t="n">
-        <v>-100826400</v>
+        <v>-114964800</v>
       </c>
       <c r="J67" s="18" t="inlineStr">
         <is>
-          <t>0.69%→0.35%</t>
+          <t>0.77%→0.39%</t>
         </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
@@ -2420,11 +2422,11 @@
         <v>10</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>138460000</v>
+        <v>147490000</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>5.66%→6.03%</t>
+          <t>5.92%→6.30%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
@@ -2441,11 +2443,11 @@
         <v>-12</v>
       </c>
       <c r="I68" s="17" t="n">
-        <v>-133644000</v>
+        <v>-132096000</v>
       </c>
       <c r="J68" s="18" t="inlineStr">
         <is>
-          <t>1.31%→0.84%</t>
+          <t>1.27%→0.82%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
@@ -2464,11 +2466,11 @@
         <v>3</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>159960000</v>
+        <v>162540000</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>5.54%→5.98%</t>
+          <t>5.52%→5.96%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">

--- a/reports/pdf_change_20261022.xlsx
+++ b/reports/pdf_change_20261022.xlsx
@@ -1111,23 +1111,23 @@
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
-          <t>에이치브이엠  (편출)</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H23" s="17" t="n">
         <v>-50</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>-2118505320</v>
+        <v>-2746455416</v>
       </c>
       <c r="J23" s="18" t="inlineStr">
         <is>
-          <t>0.94%→0.00%</t>
+          <t>4.36%→3.08%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>180→130</t>
         </is>
       </c>
     </row>
@@ -1155,23 +1155,23 @@
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에이치브이엠  (편출)</t>
         </is>
       </c>
       <c r="H24" s="17" t="n">
         <v>-50</v>
       </c>
       <c r="I24" s="17" t="n">
-        <v>-2746455416</v>
+        <v>-2118505320</v>
       </c>
       <c r="J24" s="18" t="inlineStr">
         <is>
-          <t>4.36%→3.08%</t>
+          <t>0.94%→0.00%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>180→130</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -1243,23 +1243,23 @@
       </c>
       <c r="G26" s="16" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H26" s="17" t="n">
         <v>-40</v>
       </c>
       <c r="I26" s="17" t="n">
-        <v>-7191681088</v>
+        <v>-3175444480</v>
       </c>
       <c r="J26" s="18" t="inlineStr">
         <is>
-          <t>4.62%→1.55%</t>
+          <t>4.46%→3.09%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>60→20</t>
+          <t>130→90</t>
         </is>
       </c>
     </row>
@@ -1287,23 +1287,23 @@
       </c>
       <c r="G27" s="16" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H27" s="17" t="n">
         <v>-40</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>-3175444480</v>
+        <v>-7191681088</v>
       </c>
       <c r="J27" s="18" t="inlineStr">
         <is>
-          <t>4.46%→3.09%</t>
+          <t>4.62%→1.55%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>130→90</t>
+          <t>60→20</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20261022.xlsx
+++ b/reports/pdf_change_20261022.xlsx
@@ -1111,23 +1111,23 @@
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에이치브이엠  (편출)</t>
         </is>
       </c>
       <c r="H23" s="17" t="n">
         <v>-50</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>-2746455416</v>
+        <v>-2118505320</v>
       </c>
       <c r="J23" s="18" t="inlineStr">
         <is>
-          <t>4.36%→3.08%</t>
+          <t>0.94%→0.00%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>180→130</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -1155,23 +1155,23 @@
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
-          <t>에이치브이엠  (편출)</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H24" s="17" t="n">
         <v>-50</v>
       </c>
       <c r="I24" s="17" t="n">
-        <v>-2118505320</v>
+        <v>-2746455416</v>
       </c>
       <c r="J24" s="18" t="inlineStr">
         <is>
-          <t>0.94%→0.00%</t>
+          <t>4.36%→3.08%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>180→130</t>
         </is>
       </c>
     </row>
@@ -1243,23 +1243,23 @@
       </c>
       <c r="G26" s="16" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H26" s="17" t="n">
         <v>-40</v>
       </c>
       <c r="I26" s="17" t="n">
-        <v>-3175444480</v>
+        <v>-7191681088</v>
       </c>
       <c r="J26" s="18" t="inlineStr">
         <is>
-          <t>4.46%→3.09%</t>
+          <t>4.62%→1.55%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>130→90</t>
+          <t>60→20</t>
         </is>
       </c>
     </row>
@@ -1287,23 +1287,23 @@
       </c>
       <c r="G27" s="16" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H27" s="17" t="n">
         <v>-40</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>-7191681088</v>
+        <v>-3175444480</v>
       </c>
       <c r="J27" s="18" t="inlineStr">
         <is>
-          <t>4.62%→1.55%</t>
+          <t>4.46%→3.09%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>60→20</t>
+          <t>130→90</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20261022.xlsx
+++ b/reports/pdf_change_20261022.xlsx
@@ -1111,23 +1111,23 @@
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에이치브이엠  (편출)</t>
         </is>
       </c>
       <c r="H23" s="17" t="n">
         <v>-50</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>-2746455416</v>
+        <v>-2118505320</v>
       </c>
       <c r="J23" s="18" t="inlineStr">
         <is>
-          <t>4.36%→3.08%</t>
+          <t>0.94%→0.00%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>180→130</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -1155,23 +1155,23 @@
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
-          <t>에이치브이엠  (편출)</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H24" s="17" t="n">
         <v>-50</v>
       </c>
       <c r="I24" s="17" t="n">
-        <v>-2118505320</v>
+        <v>-2746455416</v>
       </c>
       <c r="J24" s="18" t="inlineStr">
         <is>
-          <t>0.94%→0.00%</t>
+          <t>4.36%→3.08%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>180→130</t>
         </is>
       </c>
     </row>
